--- a/stick-world/config/excel/法术科技.xlsx
+++ b/stick-world/config/excel/法术科技.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="法术科技" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="spell_techs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>#output_dir: technology</t>
+          <t>#output_dir: tech</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -508,7 +508,6 @@
           <t>elemental</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>火球术,火焰附魔</t>
@@ -536,7 +535,6 @@
           <t>elemental</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>冰箭术,冻结陷阱</t>
@@ -596,7 +594,6 @@
           <t>restoration</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>战场急救,回春术</t>
@@ -624,7 +621,6 @@
           <t>summon</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>召唤低级单位</t>
